--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_coquimbo.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,28 +408,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>63.85814</v>
+      </c>
+      <c r="C2">
+        <v>94.5831</v>
+      </c>
+      <c r="D2">
+        <v>81.55744</v>
+      </c>
+      <c r="E2">
+        <v>46.68568</v>
+      </c>
+      <c r="F2">
         <v>64.16132</v>
       </c>
-      <c r="C2">
-        <v>63.85814</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>99.25284000000001</v>
       </c>
-      <c r="E2">
-        <v>94.5831</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>103.7325</v>
       </c>
-      <c r="G2">
-        <v>81.55744</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>68.34863</v>
-      </c>
-      <c r="I2">
-        <v>46.68568</v>
       </c>
     </row>
     <row r="3">
@@ -439,28 +439,28 @@
         </is>
       </c>
       <c r="B3">
+        <v>63.55196</v>
+      </c>
+      <c r="C3">
+        <v>95.21957999999999</v>
+      </c>
+      <c r="D3">
+        <v>80.36121</v>
+      </c>
+      <c r="E3">
+        <v>43.73524</v>
+      </c>
+      <c r="F3">
         <v>63.77958</v>
       </c>
-      <c r="C3">
-        <v>63.55196</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
         <v>99.92151</v>
       </c>
-      <c r="E3">
-        <v>95.21957999999999</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>106.8903</v>
       </c>
-      <c r="G3">
-        <v>80.36121</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>64.54422</v>
-      </c>
-      <c r="I3">
-        <v>43.73524</v>
       </c>
     </row>
     <row r="4">
@@ -473,25 +473,25 @@
         <v>63.66782</v>
       </c>
       <c r="C4">
+        <v>98.07956</v>
+      </c>
+      <c r="D4">
+        <v>83.14764</v>
+      </c>
+      <c r="E4">
+        <v>42.82116</v>
+      </c>
+      <c r="F4">
         <v>63.66782</v>
       </c>
-      <c r="D4">
+      <c r="G4">
         <v>102.8121</v>
       </c>
-      <c r="E4">
-        <v>98.07956</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>99.44289000000001</v>
       </c>
-      <c r="G4">
-        <v>83.14764</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>58.69018</v>
-      </c>
-      <c r="I4">
-        <v>42.82116</v>
       </c>
     </row>
     <row r="5">
@@ -501,28 +501,28 @@
         </is>
       </c>
       <c r="B5">
+        <v>66.08041</v>
+      </c>
+      <c r="C5">
+        <v>95.78946999999999</v>
+      </c>
+      <c r="D5">
+        <v>77.29084</v>
+      </c>
+      <c r="E5">
+        <v>21.77419</v>
+      </c>
+      <c r="F5">
         <v>66.0804</v>
       </c>
-      <c r="C5">
-        <v>66.08041</v>
-      </c>
-      <c r="D5">
+      <c r="G5">
         <v>100.9023</v>
       </c>
-      <c r="E5">
-        <v>95.78946999999999</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>101.5936</v>
       </c>
-      <c r="G5">
-        <v>77.29084</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>29.43548</v>
-      </c>
-      <c r="I5">
-        <v>21.77419</v>
       </c>
     </row>
     <row r="6">
@@ -532,28 +532,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>66.66667</v>
+      </c>
+      <c r="C6">
+        <v>94.49378</v>
+      </c>
+      <c r="D6">
+        <v>80.63242</v>
+      </c>
+      <c r="E6">
+        <v>35.52631</v>
+      </c>
+      <c r="F6">
         <v>66.96696</v>
       </c>
-      <c r="C6">
-        <v>66.66667</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>101.9538</v>
       </c>
-      <c r="E6">
-        <v>94.49378</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>132.8063</v>
       </c>
-      <c r="G6">
-        <v>80.63242</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>43.79699</v>
-      </c>
-      <c r="I6">
-        <v>35.52631</v>
       </c>
     </row>
     <row r="7">
@@ -563,28 +563,28 @@
         </is>
       </c>
       <c r="B7">
+        <v>66.36604</v>
+      </c>
+      <c r="C7">
+        <v>96.11145</v>
+      </c>
+      <c r="D7">
+        <v>78.58508999999999</v>
+      </c>
+      <c r="E7">
+        <v>34.19952</v>
+      </c>
+      <c r="F7">
         <v>66.57825</v>
       </c>
-      <c r="C7">
-        <v>66.36604</v>
-      </c>
-      <c r="D7">
+      <c r="G7">
         <v>106.4605</v>
       </c>
-      <c r="E7">
-        <v>96.11145</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>127.2148</v>
       </c>
-      <c r="G7">
-        <v>78.58508999999999</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>45.93787</v>
-      </c>
-      <c r="I7">
-        <v>34.19952</v>
       </c>
     </row>
     <row r="8">
@@ -594,28 +594,28 @@
         </is>
       </c>
       <c r="B8">
+        <v>71.10518999999999</v>
+      </c>
+      <c r="C8">
+        <v>96.72221999999999</v>
+      </c>
+      <c r="D8">
+        <v>83.52155999999999</v>
+      </c>
+      <c r="E8">
+        <v>36.00829</v>
+      </c>
+      <c r="F8">
         <v>71.32711999999999</v>
       </c>
-      <c r="C8">
-        <v>71.10518999999999</v>
-      </c>
-      <c r="D8">
+      <c r="G8">
         <v>101.5833</v>
       </c>
-      <c r="E8">
-        <v>96.72221999999999</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>105.0821</v>
       </c>
-      <c r="G8">
-        <v>83.52155999999999</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>50.28131</v>
-      </c>
-      <c r="I8">
-        <v>36.00829</v>
       </c>
     </row>
     <row r="9">
@@ -625,28 +625,28 @@
         </is>
       </c>
       <c r="B9">
+        <v>57.00935</v>
+      </c>
+      <c r="C9">
+        <v>97.14912</v>
+      </c>
+      <c r="D9">
+        <v>90.46563</v>
+      </c>
+      <c r="E9">
+        <v>36.84211</v>
+      </c>
+      <c r="F9">
         <v>57.38318</v>
       </c>
-      <c r="C9">
-        <v>57.00935</v>
-      </c>
-      <c r="D9">
+      <c r="G9">
         <v>99.89035</v>
       </c>
-      <c r="E9">
-        <v>97.14912</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>105.5432</v>
       </c>
-      <c r="G9">
-        <v>90.46563</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>50.06419</v>
-      </c>
-      <c r="I9">
-        <v>36.84211</v>
       </c>
     </row>
     <row r="10">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="B10">
+        <v>61.8677</v>
+      </c>
+      <c r="C10">
+        <v>96.30817999999999</v>
+      </c>
+      <c r="D10">
+        <v>81.71141</v>
+      </c>
+      <c r="E10">
+        <v>34.94487</v>
+      </c>
+      <c r="F10">
         <v>61.99741</v>
       </c>
-      <c r="C10">
-        <v>61.8677</v>
-      </c>
-      <c r="D10">
+      <c r="G10">
         <v>100.8026</v>
       </c>
-      <c r="E10">
-        <v>96.30817999999999</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>99.41275</v>
       </c>
-      <c r="G10">
-        <v>81.71141</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>49.57591</v>
-      </c>
-      <c r="I10">
-        <v>34.94487</v>
       </c>
     </row>
     <row r="11">
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="B11">
+        <v>65.04956</v>
+      </c>
+      <c r="C11">
+        <v>95.77911</v>
+      </c>
+      <c r="D11">
+        <v>85.63502</v>
+      </c>
+      <c r="E11">
+        <v>38.47481</v>
+      </c>
+      <c r="F11">
         <v>65.20605</v>
       </c>
-      <c r="C11">
-        <v>65.04956</v>
-      </c>
-      <c r="D11">
+      <c r="G11">
         <v>99.36528</v>
       </c>
-      <c r="E11">
-        <v>95.77911</v>
-      </c>
-      <c r="F11">
+      <c r="H11">
         <v>103.5758</v>
       </c>
-      <c r="G11">
-        <v>85.63502</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>54.00276</v>
-      </c>
-      <c r="I11">
-        <v>38.47481</v>
       </c>
     </row>
     <row r="12">
@@ -718,28 +718,28 @@
         </is>
       </c>
       <c r="B12">
+        <v>64.85411000000001</v>
+      </c>
+      <c r="C12">
+        <v>96.71084</v>
+      </c>
+      <c r="D12">
+        <v>84.55986</v>
+      </c>
+      <c r="E12">
+        <v>37.67372</v>
+      </c>
+      <c r="F12">
         <v>64.97347000000001</v>
       </c>
-      <c r="C12">
-        <v>64.85411000000001</v>
-      </c>
-      <c r="D12">
+      <c r="G12">
         <v>100.5612</v>
       </c>
-      <c r="E12">
-        <v>96.71084</v>
-      </c>
-      <c r="F12">
+      <c r="H12">
         <v>103.3893</v>
       </c>
-      <c r="G12">
-        <v>84.55986</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
         <v>51.23973</v>
-      </c>
-      <c r="I12">
-        <v>37.67372</v>
       </c>
     </row>
     <row r="13">
@@ -749,28 +749,28 @@
         </is>
       </c>
       <c r="B13">
+        <v>56.59204</v>
+      </c>
+      <c r="C13">
+        <v>97.24038</v>
+      </c>
+      <c r="D13">
+        <v>88.95435000000001</v>
+      </c>
+      <c r="E13">
+        <v>40.62059</v>
+      </c>
+      <c r="F13">
         <v>56.71642</v>
       </c>
-      <c r="C13">
-        <v>56.59204</v>
-      </c>
-      <c r="D13">
+      <c r="G13">
         <v>100.5084</v>
       </c>
-      <c r="E13">
-        <v>97.24038</v>
-      </c>
-      <c r="F13">
+      <c r="H13">
         <v>104.271</v>
       </c>
-      <c r="G13">
-        <v>88.95435000000001</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
         <v>53.52609</v>
-      </c>
-      <c r="I13">
-        <v>40.62059</v>
       </c>
     </row>
     <row r="14">
@@ -780,28 +780,28 @@
         </is>
       </c>
       <c r="B14">
+        <v>59.7119</v>
+      </c>
+      <c r="C14">
+        <v>97.40931999999999</v>
+      </c>
+      <c r="D14">
+        <v>84.4267</v>
+      </c>
+      <c r="E14">
+        <v>29.74112</v>
+      </c>
+      <c r="F14">
         <v>59.75837</v>
       </c>
-      <c r="C14">
-        <v>59.7119</v>
-      </c>
-      <c r="D14">
+      <c r="G14">
         <v>102.418</v>
       </c>
-      <c r="E14">
-        <v>97.40931999999999</v>
-      </c>
-      <c r="F14">
+      <c r="H14">
         <v>102.2248</v>
       </c>
-      <c r="G14">
-        <v>84.4267</v>
-      </c>
-      <c r="H14">
+      <c r="I14">
         <v>37.77845</v>
-      </c>
-      <c r="I14">
-        <v>29.74112</v>
       </c>
     </row>
     <row r="15">
@@ -814,25 +814,25 @@
         <v>61.64053</v>
       </c>
       <c r="C15">
+        <v>96.72011999999999</v>
+      </c>
+      <c r="D15">
+        <v>85.22387999999999</v>
+      </c>
+      <c r="E15">
+        <v>38.44358</v>
+      </c>
+      <c r="F15">
         <v>61.64053</v>
       </c>
-      <c r="D15">
+      <c r="G15">
         <v>100.1458</v>
       </c>
-      <c r="E15">
-        <v>96.72011999999999</v>
-      </c>
-      <c r="F15">
+      <c r="H15">
         <v>98.50745999999999</v>
       </c>
-      <c r="G15">
-        <v>85.22387999999999</v>
-      </c>
-      <c r="H15">
+      <c r="I15">
         <v>50.27237</v>
-      </c>
-      <c r="I15">
-        <v>38.44358</v>
       </c>
     </row>
     <row r="16">
@@ -845,25 +845,25 @@
         <v>52.17391</v>
       </c>
       <c r="C16">
+        <v>96.7366</v>
+      </c>
+      <c r="D16">
+        <v>91.59663999999999</v>
+      </c>
+      <c r="E16">
+        <v>38.47981</v>
+      </c>
+      <c r="F16">
         <v>52.17391</v>
       </c>
-      <c r="D16">
+      <c r="G16">
         <v>100.4662</v>
       </c>
-      <c r="E16">
-        <v>96.7366</v>
-      </c>
-      <c r="F16">
+      <c r="H16">
         <v>104.6218</v>
       </c>
-      <c r="G16">
-        <v>91.59663999999999</v>
-      </c>
-      <c r="H16">
+      <c r="I16">
         <v>49.16865</v>
-      </c>
-      <c r="I16">
-        <v>38.47981</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:46</t>
+    <t xml:space="preserve">2026-08-02 19:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:42</t>
+    <t xml:space="preserve">2026-08-05 10:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:35</t>
+    <t xml:space="preserve">2026-08-16 09:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:47</t>
+    <t xml:space="preserve">2026-08-19 12:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 12:00</t>
+    <t xml:space="preserve">2026-08-28 11:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:26</t>
+    <t xml:space="preserve">2026-09-06 17:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
